--- a/reports/pdf_weekly_20260923.xlsx
+++ b/reports/pdf_weekly_20260923.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,836억   ·   현금 40억(0.8%)      주말 2026-09-23  vs  주초 2026-09-21      매수 9종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,836억   ·   현금 20억(0.4%)      주말 2026-09-23  vs  주초 2026-09-21      매수 9종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1115,7 +1115,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,249억   ·   현금 119억(3.6%)      주말 2026-09-23  vs  주초 2026-09-21      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,249억   ·   현금 59억(1.8%)      주말 2026-09-23  vs  주초 2026-09-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1139,7 +1139,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억   ·   현금 85억(3.2%)      주말 2026-09-23  vs  주초 2026-09-21      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억   ·   현금 43억(1.6%)      주말 2026-09-23  vs  주초 2026-09-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1163,7 +1163,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억   ·   현금 31억(1.6%)      주말 2026-09-23  vs  주초 2026-09-21      매수 3종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억   ·   현금 16억(0.8%)      주말 2026-09-23  vs  주초 2026-09-21      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1384,7 +1384,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억   ·   현금 2억(0.8%)      주말 2026-09-23  vs  주초 2026-09-21      매수 8종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억   ·   현금 1억(0.4%)      주말 2026-09-23  vs  주초 2026-09-21      매수 8종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1737,88 +1737,88 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>77518044</v>
+        <v>71883041</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>2.58%→2.84%</t>
+          <t>0.21%→0.46%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>67→74</t>
+          <t>6→13</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-62202036</v>
+        <v>-54726031</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.70%</t>
+          <t>2.47%→2.28%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>71883041</v>
+        <v>77518044</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>0.21%→0.46%</t>
+          <t>2.58%→2.84%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>6→13</t>
+          <t>67→74</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-54726031</v>
+        <v>-62202036</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2.47%→2.28%</t>
+          <t>2.92%→2.70%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260923.xlsx
+++ b/reports/pdf_weekly_20260923.xlsx
@@ -1737,23 +1737,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>71883041</v>
+        <v>77518044</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.21%→0.46%</t>
+          <t>2.58%→2.84%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>6→13</t>
+          <t>67→74</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -1781,23 +1781,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>77518044</v>
+        <v>71883041</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>2.58%→2.84%</t>
+          <t>0.21%→0.46%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>67→74</t>
+          <t>6→13</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
